--- a/IND_WB_timeseries.xlsx
+++ b/IND_WB_timeseries.xlsx
@@ -14,21 +14,114 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6" uniqueCount="6">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="37">
+  <si>
+    <t>Bank capital to assets ratio (%)</t>
+  </si>
+  <si>
+    <t>Bank nonperforming loans (% of gross loans)</t>
+  </si>
+  <si>
+    <t>Control of Corruption</t>
+  </si>
+  <si>
+    <t>Current account balance (% of GDP)</t>
+  </si>
+  <si>
+    <t>Debt (% of GDP)</t>
+  </si>
+  <si>
+    <t>Domestic credit to private sector (% of GDP)</t>
+  </si>
+  <si>
+    <t>Exports of goods and services (% of GDP)</t>
+  </si>
+  <si>
+    <t>External debt stocks (% of GNI)</t>
+  </si>
+  <si>
+    <t>External debt stocks (current US$)</t>
+  </si>
   <si>
     <t>GDP growth (annual %)</t>
   </si>
   <si>
+    <t>GDP per capita (PPP, international $)</t>
+  </si>
+  <si>
+    <t>GDP per capita (current US$)</t>
+  </si>
+  <si>
+    <t>GDP per capita growth (annual %)</t>
+  </si>
+  <si>
+    <t>Gini index</t>
+  </si>
+  <si>
+    <t>Government Effectiveness</t>
+  </si>
+  <si>
+    <t>Government consumption (% of GDP)</t>
+  </si>
+  <si>
+    <t>Government expenditure (% of GDP)</t>
+  </si>
+  <si>
+    <t>Government revenue (% of GDP)</t>
+  </si>
+  <si>
+    <t>Imports of goods and services (% of GDP)</t>
+  </si>
+  <si>
     <t>Inflation, consumer prices (annual %)</t>
   </si>
   <si>
     <t>Interest payments (% of GDP)</t>
   </si>
   <si>
+    <t>Life expectancy at birth (years)</t>
+  </si>
+  <si>
+    <t>Military expenditure (% of GDP)</t>
+  </si>
+  <si>
+    <t>Net lending/borrowing (% of GDP)</t>
+  </si>
+  <si>
+    <t>Political Stability and Absence of Violence</t>
+  </si>
+  <si>
+    <t>Population, total</t>
+  </si>
+  <si>
+    <t>Poverty headcount ratio ($2.15/day)</t>
+  </si>
+  <si>
+    <t>Regulatory Quality</t>
+  </si>
+  <si>
+    <t>Rule of Law</t>
+  </si>
+  <si>
     <t>Tax revenue (% of GDP)</t>
   </si>
   <si>
+    <t>Total reserves (current US$)</t>
+  </si>
+  <si>
+    <t>Total reserves (months of imports)</t>
+  </si>
+  <si>
+    <t>Trade openness (% of GDP)</t>
+  </si>
+  <si>
     <t>Unemployment (% labor force)</t>
+  </si>
+  <si>
+    <t>Urban population (% of total)</t>
+  </si>
+  <si>
+    <t>Voice and Accountability</t>
   </si>
   <si>
     <t>date</t>
@@ -389,12 +482,12 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F26"/>
+  <dimension ref="A1:AK26"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:6">
+    <row r="1" spans="1:37">
       <c r="A1" s="1" t="s">
-        <v>5</v>
+        <v>36</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>0</v>
@@ -411,475 +504,2587 @@
       <c r="F1" s="1" t="s">
         <v>4</v>
       </c>
+      <c r="G1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="N1" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="O1" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="P1" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="Q1" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="R1" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="S1" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="T1" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="U1" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="V1" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="W1" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="X1" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="Y1" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="Z1" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="AA1" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="AB1" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AC1" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="AD1" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="AE1" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="AF1" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="AG1" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="AH1" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="AI1" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="AJ1" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="AK1" s="1" t="s">
+        <v>35</v>
+      </c>
     </row>
-    <row r="2" spans="1:6">
+    <row r="2" spans="1:37">
       <c r="A2" s="1">
         <v>2000</v>
       </c>
-      <c r="B2">
+      <c r="D2">
+        <v>-0.403301805257797</v>
+      </c>
+      <c r="E2">
+        <v>-0.982342580017138</v>
+      </c>
+      <c r="F2">
+        <v>55.0042464964554</v>
+      </c>
+      <c r="G2">
+        <v>28.3395511575183</v>
+      </c>
+      <c r="H2">
+        <v>12.9972363113479</v>
+      </c>
+      <c r="I2">
+        <v>21.8228803066691</v>
+      </c>
+      <c r="J2">
+        <v>101131491179.6</v>
+      </c>
+      <c r="K2">
         <v>3.84099115659129</v>
       </c>
-      <c r="C2">
+      <c r="L2">
+        <v>2090.85806894486</v>
+      </c>
+      <c r="M2">
+        <v>442.750218937263</v>
+      </c>
+      <c r="N2">
+        <v>1.90763005816579</v>
+      </c>
+      <c r="P2">
+        <v>-0.187351524829865</v>
+      </c>
+      <c r="Q2">
+        <v>11.9478354691139</v>
+      </c>
+      <c r="R2">
+        <v>15.4104025952684</v>
+      </c>
+      <c r="S2">
+        <v>11.7034288840812</v>
+      </c>
+      <c r="T2">
+        <v>13.9036865990995</v>
+      </c>
+      <c r="U2">
         <v>4.00943591045191</v>
       </c>
-      <c r="D2">
+      <c r="V2">
         <v>29.6480827255773</v>
       </c>
-      <c r="E2">
+      <c r="W2">
+        <v>62.749</v>
+      </c>
+      <c r="X2">
+        <v>2.94892990622572</v>
+      </c>
+      <c r="Y2">
+        <v>-3.81029698727217</v>
+      </c>
+      <c r="Z2">
+        <v>-1.00120759010315</v>
+      </c>
+      <c r="AA2">
+        <v>1057922733</v>
+      </c>
+      <c r="AC2">
+        <v>-0.159504070878029</v>
+      </c>
+      <c r="AD2">
+        <v>0.348079591989517</v>
+      </c>
+      <c r="AE2">
         <v>8.81014349636308</v>
       </c>
-      <c r="F2">
+      <c r="AF2">
+        <v>41059061574.6632</v>
+      </c>
+      <c r="AG2">
+        <v>6.1214797944893</v>
+      </c>
+      <c r="AH2">
+        <v>26.9009229104474</v>
+      </c>
+      <c r="AI2">
         <v>7.624</v>
       </c>
+      <c r="AJ2">
+        <v>27.667</v>
+      </c>
+      <c r="AK2">
+        <v>0.35206338763237</v>
+      </c>
     </row>
-    <row r="3" spans="1:6">
+    <row r="3" spans="1:37">
       <c r="A3" s="1">
         <v>2001</v>
       </c>
-      <c r="B3">
+      <c r="E3">
+        <v>0.290495460210207</v>
+      </c>
+      <c r="F3">
+        <v>59.0179097968845</v>
+      </c>
+      <c r="G3">
+        <v>28.6194154254102</v>
+      </c>
+      <c r="H3">
+        <v>12.5583796339108</v>
+      </c>
+      <c r="I3">
+        <v>20.6760979408451</v>
+      </c>
+      <c r="J3">
+        <v>99500093585.5</v>
+      </c>
+      <c r="K3">
         <v>4.82396626555771</v>
       </c>
-      <c r="C3">
+      <c r="L3">
+        <v>2199.53910446478</v>
+      </c>
+      <c r="M3">
+        <v>450.357900514128</v>
+      </c>
+      <c r="N3">
+        <v>2.88134658268626</v>
+      </c>
+      <c r="Q3">
+        <v>11.7614498890899</v>
+      </c>
+      <c r="R3">
+        <v>15.5456255204777</v>
+      </c>
+      <c r="S3">
+        <v>11.0400508601551</v>
+      </c>
+      <c r="T3">
+        <v>13.4348751195257</v>
+      </c>
+      <c r="U3">
         <v>3.77929312235638</v>
       </c>
-      <c r="D3">
+      <c r="V3">
         <v>29.2710304262904</v>
       </c>
-      <c r="E3">
+      <c r="W3">
+        <v>63.158</v>
+      </c>
+      <c r="X3">
+        <v>2.9244355462896</v>
+      </c>
+      <c r="Y3">
+        <v>-4.3480533950568</v>
+      </c>
+      <c r="AA3">
+        <v>1077898575</v>
+      </c>
+      <c r="AE3">
         <v>8.079454444569571</v>
       </c>
-      <c r="F3">
+      <c r="AF3">
+        <v>49050841138.7213</v>
+      </c>
+      <c r="AG3">
+        <v>7.45295243694093</v>
+      </c>
+      <c r="AH3">
+        <v>25.9932547534365</v>
+      </c>
+      <c r="AI3">
         <v>7.653</v>
       </c>
+      <c r="AJ3">
+        <v>27.918</v>
+      </c>
     </row>
-    <row r="4" spans="1:6">
+    <row r="4" spans="1:37">
       <c r="A4" s="1">
         <v>2002</v>
       </c>
-      <c r="B4">
+      <c r="D4">
+        <v>-0.5553824901580811</v>
+      </c>
+      <c r="E4">
+        <v>1.37093793900847</v>
+      </c>
+      <c r="F4">
+        <v>62.5527712945573</v>
+      </c>
+      <c r="G4">
+        <v>32.3064890735537</v>
+      </c>
+      <c r="H4">
+        <v>14.2643839243147</v>
+      </c>
+      <c r="I4">
+        <v>20.6731997171964</v>
+      </c>
+      <c r="J4">
+        <v>105741601402</v>
+      </c>
+      <c r="K4">
         <v>3.80397532112175</v>
       </c>
-      <c r="C4">
+      <c r="L4">
+        <v>2277.06974775051</v>
+      </c>
+      <c r="M4">
+        <v>469.149928973927</v>
+      </c>
+      <c r="N4">
+        <v>1.94070548515326</v>
+      </c>
+      <c r="P4">
+        <v>-0.189068421721458</v>
+      </c>
+      <c r="Q4">
+        <v>11.3140950692424</v>
+      </c>
+      <c r="R4">
+        <v>16.0529482126794</v>
+      </c>
+      <c r="S4">
+        <v>11.5941347100743</v>
+      </c>
+      <c r="T4">
+        <v>15.2442790107467</v>
+      </c>
+      <c r="U4">
         <v>4.29715203929563</v>
       </c>
-      <c r="D4">
+      <c r="V4">
         <v>28.6908516561786</v>
       </c>
-      <c r="E4">
+      <c r="W4">
+        <v>63.649</v>
+      </c>
+      <c r="X4">
+        <v>2.82686683045838</v>
+      </c>
+      <c r="Y4">
+        <v>-4.66165278845976</v>
+      </c>
+      <c r="Z4">
+        <v>-1.21066498756409</v>
+      </c>
+      <c r="AA4">
+        <v>1097600380</v>
+      </c>
+      <c r="AC4">
+        <v>-0.381400048732758</v>
+      </c>
+      <c r="AD4">
+        <v>-0.0173958707600832</v>
+      </c>
+      <c r="AE4">
         <v>8.67627393090217</v>
       </c>
-      <c r="F4">
+      <c r="AF4">
+        <v>71607865093.6969</v>
+      </c>
+      <c r="AG4">
+        <v>10.3730834871592</v>
+      </c>
+      <c r="AH4">
+        <v>29.5086629350614</v>
+      </c>
+      <c r="AI4">
         <v>7.753</v>
       </c>
+      <c r="AJ4">
+        <v>28.244</v>
+      </c>
+      <c r="AK4">
+        <v>0.426245898008347</v>
+      </c>
     </row>
-    <row r="5" spans="1:6">
+    <row r="5" spans="1:37">
       <c r="A5" s="1">
         <v>2003</v>
       </c>
-      <c r="B5">
+      <c r="D5">
+        <v>-0.456320524215698</v>
+      </c>
+      <c r="E5">
+        <v>1.44355773291234</v>
+      </c>
+      <c r="F5">
+        <v>62.1900538960464</v>
+      </c>
+      <c r="G5">
+        <v>31.6262656186491</v>
+      </c>
+      <c r="H5">
+        <v>14.9479138581734</v>
+      </c>
+      <c r="I5">
+        <v>19.7091758741244</v>
+      </c>
+      <c r="J5">
+        <v>118884622369.5</v>
+      </c>
+      <c r="K5">
         <v>7.8603814759073</v>
       </c>
-      <c r="C5">
+      <c r="L5">
+        <v>2461.48251610861</v>
+      </c>
+      <c r="M5">
+        <v>544.143133545002</v>
+      </c>
+      <c r="N5">
+        <v>6.00579964314747</v>
+      </c>
+      <c r="P5">
+        <v>-0.143909424543381</v>
+      </c>
+      <c r="Q5">
+        <v>10.8762099129119</v>
+      </c>
+      <c r="R5">
+        <v>15.5775937222978</v>
+      </c>
+      <c r="S5">
+        <v>11.8531218371758</v>
+      </c>
+      <c r="T5">
+        <v>15.6445222747346</v>
+      </c>
+      <c r="U5">
         <v>3.8058589952885</v>
       </c>
-      <c r="D5">
+      <c r="V5">
         <v>27.6162102393284</v>
       </c>
-      <c r="E5">
+      <c r="W5">
+        <v>64.086</v>
+      </c>
+      <c r="X5">
+        <v>2.67777693222748</v>
+      </c>
+      <c r="Y5">
+        <v>-3.43004355011113</v>
+      </c>
+      <c r="Z5">
+        <v>-1.50999701023102</v>
+      </c>
+      <c r="AA5">
+        <v>1116803006</v>
+      </c>
+      <c r="AC5">
+        <v>-0.381630450487137</v>
+      </c>
+      <c r="AD5">
+        <v>0.120161645114422</v>
+      </c>
+      <c r="AE5">
         <v>9.10808432214403</v>
       </c>
-      <c r="F5">
+      <c r="AF5">
+        <v>103737208055.967</v>
+      </c>
+      <c r="AG5">
+        <v>12.2832820147208</v>
+      </c>
+      <c r="AH5">
+        <v>30.592436132908</v>
+      </c>
+      <c r="AI5">
         <v>7.68</v>
       </c>
+      <c r="AJ5">
+        <v>28.572</v>
+      </c>
+      <c r="AK5">
+        <v>0.454564899206161</v>
+      </c>
     </row>
-    <row r="6" spans="1:6">
+    <row r="6" spans="1:37">
       <c r="A6" s="1">
         <v>2004</v>
       </c>
-      <c r="B6">
+      <c r="D6">
+        <v>-0.448476195335388</v>
+      </c>
+      <c r="E6">
+        <v>0.110018010197153</v>
+      </c>
+      <c r="F6">
+        <v>62.5929767433885</v>
+      </c>
+      <c r="G6">
+        <v>36.1918038545968</v>
+      </c>
+      <c r="H6">
+        <v>17.8591249630479</v>
+      </c>
+      <c r="I6">
+        <v>17.5588240572864</v>
+      </c>
+      <c r="J6">
+        <v>123644485822.1</v>
+      </c>
+      <c r="K6">
         <v>7.92293661199932</v>
       </c>
-      <c r="C6">
+      <c r="L6">
+        <v>2681.86116841254</v>
+      </c>
+      <c r="M6">
+        <v>624.258826510066</v>
+      </c>
+      <c r="N6">
+        <v>6.09996522450102</v>
+      </c>
+      <c r="O6">
+        <v>27.7</v>
+      </c>
+      <c r="P6">
+        <v>-0.179698884487152</v>
+      </c>
+      <c r="Q6">
+        <v>10.4047023481415</v>
+      </c>
+      <c r="R6">
+        <v>15.1334829998657</v>
+      </c>
+      <c r="S6">
+        <v>12.0829219683708</v>
+      </c>
+      <c r="T6">
+        <v>19.6446890963991</v>
+      </c>
+      <c r="U6">
         <v>3.76725173477515</v>
       </c>
-      <c r="D6">
+      <c r="V6">
         <v>25.6445936669826</v>
       </c>
-      <c r="E6">
+      <c r="W6">
+        <v>64.48399999999999</v>
+      </c>
+      <c r="X6">
+        <v>2.82875224798105</v>
+      </c>
+      <c r="Y6">
+        <v>-3.25615794219875</v>
+      </c>
+      <c r="Z6">
+        <v>-1.28043293952942</v>
+      </c>
+      <c r="AA6">
+        <v>1135991513</v>
+      </c>
+      <c r="AB6">
+        <v>46.4</v>
+      </c>
+      <c r="AC6">
+        <v>-0.378129839897156</v>
+      </c>
+      <c r="AD6">
+        <v>0.0533560588955879</v>
+      </c>
+      <c r="AE6">
         <v>9.57081708050975</v>
       </c>
-      <c r="F6">
+      <c r="AF6">
+        <v>131631143125.845</v>
+      </c>
+      <c r="AG6">
+        <v>11.3051095119993</v>
+      </c>
+      <c r="AH6">
+        <v>37.503814059447</v>
+      </c>
+      <c r="AI6">
         <v>7.625</v>
       </c>
+      <c r="AJ6">
+        <v>28.903</v>
+      </c>
+      <c r="AK6">
+        <v>0.39996737241745</v>
+      </c>
     </row>
-    <row r="7" spans="1:6">
+    <row r="7" spans="1:37">
       <c r="A7" s="1">
         <v>2005</v>
       </c>
       <c r="B7">
+        <v>5.22982329166892</v>
+      </c>
+      <c r="C7">
+        <v>4.40178559448821</v>
+      </c>
+      <c r="D7">
+        <v>-0.363160848617554</v>
+      </c>
+      <c r="E7">
+        <v>-1.25350400207393</v>
+      </c>
+      <c r="F7">
+        <v>62.2265261001737</v>
+      </c>
+      <c r="G7">
+        <v>40.0679804780573</v>
+      </c>
+      <c r="H7">
+        <v>19.6052466948335</v>
+      </c>
+      <c r="I7">
+        <v>14.8800140528443</v>
+      </c>
+      <c r="J7">
+        <v>121195478444.5</v>
+      </c>
+      <c r="K7">
         <v>7.92343062148318</v>
       </c>
-      <c r="C7">
+      <c r="L7">
+        <v>2936.80322011933</v>
+      </c>
+      <c r="M7">
+        <v>710.488080408949</v>
+      </c>
+      <c r="N7">
+        <v>6.17702892486365</v>
+      </c>
+      <c r="P7">
+        <v>-0.0987746343016624</v>
+      </c>
+      <c r="Q7">
+        <v>10.3661401972455</v>
+      </c>
+      <c r="R7">
+        <v>15.1739835903438</v>
+      </c>
+      <c r="S7">
+        <v>12.3350942450845</v>
+      </c>
+      <c r="T7">
+        <v>22.3964229200356</v>
+      </c>
+      <c r="U7">
         <v>4.24634362031923</v>
       </c>
-      <c r="D7">
+      <c r="V7">
         <v>23.3823470709695</v>
       </c>
-      <c r="E7">
+      <c r="W7">
+        <v>64.93899999999999</v>
+      </c>
+      <c r="X7">
+        <v>2.91058750164482</v>
+      </c>
+      <c r="Y7">
+        <v>-3.23146948310993</v>
+      </c>
+      <c r="Z7">
+        <v>-1.01388049125671</v>
+      </c>
+      <c r="AA7">
+        <v>1154676322</v>
+      </c>
+      <c r="AC7">
+        <v>-0.291889518499374</v>
+      </c>
+      <c r="AD7">
+        <v>0.13313016295433</v>
+      </c>
+      <c r="AE7">
         <v>10.0809315263538</v>
       </c>
-      <c r="F7">
+      <c r="AF7">
+        <v>137824828256.285</v>
+      </c>
+      <c r="AG7">
+        <v>8.518473171846161</v>
+      </c>
+      <c r="AH7">
+        <v>42.0016696148691</v>
+      </c>
+      <c r="AI7">
         <v>7.552</v>
       </c>
+      <c r="AJ7">
+        <v>29.235</v>
+      </c>
+      <c r="AK7">
+        <v>0.413685649633408</v>
+      </c>
     </row>
-    <row r="8" spans="1:6">
+    <row r="8" spans="1:37">
       <c r="A8" s="1">
         <v>2006</v>
       </c>
-      <c r="B8">
+      <c r="D8">
+        <v>-0.274562805891037</v>
+      </c>
+      <c r="E8">
+        <v>-0.988988302952292</v>
+      </c>
+      <c r="F8">
+        <v>59.6667302762217</v>
+      </c>
+      <c r="G8">
+        <v>43.6277524334268</v>
+      </c>
+      <c r="H8">
+        <v>21.2679414221966</v>
+      </c>
+      <c r="I8">
+        <v>17.0996791242773</v>
+      </c>
+      <c r="J8">
+        <v>159525518911.4</v>
+      </c>
+      <c r="K8">
         <v>8.060732571666509</v>
       </c>
-      <c r="C8">
+      <c r="L8">
+        <v>3220.62692939401</v>
+      </c>
+      <c r="M8">
+        <v>801.668353659022</v>
+      </c>
+      <c r="N8">
+        <v>6.38367720854581</v>
+      </c>
+      <c r="P8">
+        <v>-0.0953764915466309</v>
+      </c>
+      <c r="Q8">
+        <v>9.80247046783494</v>
+      </c>
+      <c r="R8">
+        <v>15.1894795636765</v>
+      </c>
+      <c r="S8">
+        <v>13.3167898343502</v>
+      </c>
+      <c r="T8">
+        <v>24.4565390770687</v>
+      </c>
+      <c r="U8">
         <v>5.79652337561633</v>
       </c>
-      <c r="D8">
+      <c r="V8">
         <v>22.5783590403803</v>
       </c>
-      <c r="E8">
+      <c r="W8">
+        <v>65.373</v>
+      </c>
+      <c r="X8">
+        <v>2.68038156022763</v>
+      </c>
+      <c r="Y8">
+        <v>-2.26402820004874</v>
+      </c>
+      <c r="Z8">
+        <v>-1.06518423557281</v>
+      </c>
+      <c r="AA8">
+        <v>1172878890</v>
+      </c>
+      <c r="AC8">
+        <v>-0.283315151929855</v>
+      </c>
+      <c r="AD8">
+        <v>0.178989619016647</v>
+      </c>
+      <c r="AE8">
         <v>11.1293370539779</v>
       </c>
-      <c r="F8">
+      <c r="AF8">
+        <v>178049790065.97</v>
+      </c>
+      <c r="AG8">
+        <v>8.91992866511892</v>
+      </c>
+      <c r="AH8">
+        <v>45.7244804992652</v>
+      </c>
+      <c r="AI8">
         <v>7.552</v>
       </c>
+      <c r="AJ8">
+        <v>29.569</v>
+      </c>
+      <c r="AK8">
+        <v>0.437193721532822</v>
+      </c>
     </row>
-    <row r="9" spans="1:6">
+    <row r="9" spans="1:37">
       <c r="A9" s="1">
         <v>2007</v>
       </c>
-      <c r="B9">
+      <c r="D9">
+        <v>-0.397690296173096</v>
+      </c>
+      <c r="E9">
+        <v>-0.66371764877261</v>
+      </c>
+      <c r="F9">
+        <v>57.4975363892468</v>
+      </c>
+      <c r="G9">
+        <v>45.6277647457138</v>
+      </c>
+      <c r="H9">
+        <v>20.7996997489032</v>
+      </c>
+      <c r="I9">
+        <v>16.8414102457773</v>
+      </c>
+      <c r="J9">
+        <v>204057539299.5</v>
+      </c>
+      <c r="K9">
         <v>7.6608150670107</v>
       </c>
-      <c r="C9">
+      <c r="L9">
+        <v>3508.06183171605</v>
+      </c>
+      <c r="M9">
+        <v>1021.88707706826</v>
+      </c>
+      <c r="N9">
+        <v>6.05160013740698</v>
+      </c>
+      <c r="P9">
+        <v>0.136991709470749</v>
+      </c>
+      <c r="Q9">
+        <v>9.862115728426421</v>
+      </c>
+      <c r="R9">
+        <v>15.2578600235571</v>
+      </c>
+      <c r="S9">
+        <v>14.4395957808587</v>
+      </c>
+      <c r="T9">
+        <v>24.8865689304448</v>
+      </c>
+      <c r="U9">
         <v>6.37288135593232</v>
       </c>
-      <c r="D9">
+      <c r="V9">
         <v>22.2020494199465</v>
       </c>
-      <c r="E9">
+      <c r="W9">
+        <v>65.803</v>
+      </c>
+      <c r="X9">
+        <v>2.47824652803557</v>
+      </c>
+      <c r="Y9">
+        <v>-0.479110412536923</v>
+      </c>
+      <c r="Z9">
+        <v>-1.15429580211639</v>
+      </c>
+      <c r="AA9">
+        <v>1190676021</v>
+      </c>
+      <c r="AC9">
+        <v>-0.313716232776642</v>
+      </c>
+      <c r="AD9">
+        <v>0.0968981608748436</v>
+      </c>
+      <c r="AE9">
         <v>12.1083469904149</v>
       </c>
-      <c r="F9">
+      <c r="AF9">
+        <v>276578100117.408</v>
+      </c>
+      <c r="AG9">
+        <v>11.1391919314526</v>
+      </c>
+      <c r="AH9">
+        <v>45.686268679348</v>
+      </c>
+      <c r="AI9">
         <v>7.561</v>
       </c>
+      <c r="AJ9">
+        <v>29.906</v>
+      </c>
+      <c r="AK9">
+        <v>0.453963935375214</v>
+      </c>
     </row>
-    <row r="10" spans="1:6">
+    <row r="10" spans="1:37">
       <c r="A10" s="1">
         <v>2008</v>
       </c>
       <c r="B10">
+        <v>6.32558822247969</v>
+      </c>
+      <c r="C10">
+        <v>2.44971206075607</v>
+      </c>
+      <c r="D10">
+        <v>-0.33909797668457</v>
+      </c>
+      <c r="E10">
+        <v>-2.58337749259838</v>
+      </c>
+      <c r="F10">
+        <v>57.2922142809949</v>
+      </c>
+      <c r="G10">
+        <v>49.559366687116</v>
+      </c>
+      <c r="H10">
+        <v>24.0973572601391</v>
+      </c>
+      <c r="I10">
+        <v>19.0572058938661</v>
+      </c>
+      <c r="J10">
+        <v>227111768434.6</v>
+      </c>
+      <c r="K10">
         <v>3.08669805921981</v>
       </c>
-      <c r="C10">
+      <c r="L10">
+        <v>3633.36783240716</v>
+      </c>
+      <c r="M10">
+        <v>992.519584923828</v>
+      </c>
+      <c r="N10">
+        <v>1.61413451702882</v>
+      </c>
+      <c r="P10">
+        <v>-0.009732914157211781</v>
+      </c>
+      <c r="Q10">
+        <v>10.5384811563533</v>
+      </c>
+      <c r="R10">
+        <v>17.2276704329522</v>
+      </c>
+      <c r="S10">
+        <v>12.7597307966559</v>
+      </c>
+      <c r="T10">
+        <v>29.2708631790835</v>
+      </c>
+      <c r="U10">
         <v>8.349267049075809</v>
       </c>
-      <c r="D10">
+      <c r="V10">
         <v>19.7338835319382</v>
       </c>
-      <c r="E10">
+      <c r="W10">
+        <v>66.247</v>
+      </c>
+      <c r="X10">
+        <v>2.63146078124112</v>
+      </c>
+      <c r="Y10">
+        <v>-4.97258655315357</v>
+      </c>
+      <c r="Z10">
+        <v>-1.10970735549927</v>
+      </c>
+      <c r="AA10">
+        <v>1207930964</v>
+      </c>
+      <c r="AC10">
+        <v>-0.41364324092865</v>
+      </c>
+      <c r="AD10">
+        <v>0.0958504602313042</v>
+      </c>
+      <c r="AE10">
         <v>10.9771721522223</v>
       </c>
-      <c r="F10">
+      <c r="AF10">
+        <v>257422725614.879</v>
+      </c>
+      <c r="AG10">
+        <v>7.71425265694142</v>
+      </c>
+      <c r="AH10">
+        <v>53.3682204392226</v>
+      </c>
+      <c r="AI10">
         <v>7.656</v>
       </c>
+      <c r="AJ10">
+        <v>30.246</v>
+      </c>
+      <c r="AK10">
+        <v>0.462193101644516</v>
+      </c>
     </row>
-    <row r="11" spans="1:6">
+    <row r="11" spans="1:37">
       <c r="A11" s="1">
         <v>2009</v>
       </c>
-      <c r="B11">
+      <c r="D11">
+        <v>-0.452406287193298</v>
+      </c>
+      <c r="E11">
+        <v>-1.95146209111802</v>
+      </c>
+      <c r="F11">
+        <v>55.2564461117969</v>
+      </c>
+      <c r="G11">
+        <v>48.1244479112046</v>
+      </c>
+      <c r="H11">
+        <v>20.4005193743564</v>
+      </c>
+      <c r="I11">
+        <v>19.2155611185983</v>
+      </c>
+      <c r="J11">
+        <v>256312241333.4</v>
+      </c>
+      <c r="K11">
         <v>7.86188883286074</v>
       </c>
-      <c r="C11">
+      <c r="L11">
+        <v>3886.58197693247</v>
+      </c>
+      <c r="M11">
+        <v>1094.94974598436</v>
+      </c>
+      <c r="N11">
+        <v>6.31340985793889</v>
+      </c>
+      <c r="O11">
+        <v>27.8</v>
+      </c>
+      <c r="P11">
+        <v>-0.00329578877426684</v>
+      </c>
+      <c r="Q11">
+        <v>11.459667419691</v>
+      </c>
+      <c r="R11">
+        <v>16.8518927116001</v>
+      </c>
+      <c r="S11">
+        <v>11.4202885918772</v>
+      </c>
+      <c r="T11">
+        <v>25.8723502685274</v>
+      </c>
+      <c r="U11">
         <v>10.8823529411764</v>
       </c>
-      <c r="D11">
+      <c r="V11">
         <v>19.3722386891113</v>
       </c>
-      <c r="E11">
+      <c r="W11">
+        <v>66.7</v>
+      </c>
+      <c r="X11">
+        <v>3.12938472737472</v>
+      </c>
+      <c r="Y11">
+        <v>-5.51353416873553</v>
+      </c>
+      <c r="Z11">
+        <v>-1.35554790496826</v>
+      </c>
+      <c r="AA11">
+        <v>1225524753</v>
+      </c>
+      <c r="AB11">
+        <v>34.6</v>
+      </c>
+      <c r="AC11">
+        <v>-0.349533259868622</v>
+      </c>
+      <c r="AD11">
+        <v>0.0179808251559734</v>
+      </c>
+      <c r="AE11">
         <v>9.80972540638804</v>
       </c>
-      <c r="F11">
+      <c r="AF11">
+        <v>284682887897.586</v>
+      </c>
+      <c r="AG11">
+        <v>9.773711143144499</v>
+      </c>
+      <c r="AH11">
+        <v>46.2728696428837</v>
+      </c>
+      <c r="AI11">
         <v>7.664</v>
       </c>
+      <c r="AJ11">
+        <v>30.587</v>
+      </c>
+      <c r="AK11">
+        <v>0.460749089717865</v>
+      </c>
     </row>
-    <row r="12" spans="1:6">
+    <row r="12" spans="1:37">
       <c r="A12" s="1">
         <v>2010</v>
       </c>
-      <c r="B12">
+      <c r="D12">
+        <v>-0.463754564523697</v>
+      </c>
+      <c r="E12">
+        <v>-3.25348368945179</v>
+      </c>
+      <c r="F12">
+        <v>51.5919103003897</v>
+      </c>
+      <c r="G12">
+        <v>50.5553749785224</v>
+      </c>
+      <c r="H12">
+        <v>22.4009332487945</v>
+      </c>
+      <c r="I12">
+        <v>17.520327243228</v>
+      </c>
+      <c r="J12">
+        <v>290427544563.2</v>
+      </c>
+      <c r="K12">
         <v>8.49758470221235</v>
       </c>
-      <c r="C12">
+      <c r="L12">
+        <v>4206.45986002117</v>
+      </c>
+      <c r="M12">
+        <v>1347.51939071367</v>
+      </c>
+      <c r="N12">
+        <v>6.93079780415253</v>
+      </c>
+      <c r="P12">
+        <v>0.0316559858620167</v>
+      </c>
+      <c r="Q12">
+        <v>11.0076078674499</v>
+      </c>
+      <c r="R12">
+        <v>16.5051359514049</v>
+      </c>
+      <c r="S12">
+        <v>13.1835965373763</v>
+      </c>
+      <c r="T12">
+        <v>26.8542732486216</v>
+      </c>
+      <c r="U12">
         <v>11.9893899204244</v>
       </c>
-      <c r="D12">
+      <c r="V12">
         <v>18.2806647197003</v>
       </c>
-      <c r="E12">
+      <c r="W12">
+        <v>67.16200000000001</v>
+      </c>
+      <c r="X12">
+        <v>2.88946327164641</v>
+      </c>
+      <c r="Y12">
+        <v>-3.48058118972693</v>
+      </c>
+      <c r="Z12">
+        <v>-1.27798449993134</v>
+      </c>
+      <c r="AA12">
+        <v>1243481564</v>
+      </c>
+      <c r="AC12">
+        <v>-0.41047203540802</v>
+      </c>
+      <c r="AD12">
+        <v>-0.0358108207583427</v>
+      </c>
+      <c r="AE12">
         <v>10.3880397905312</v>
       </c>
-      <c r="F12">
+      <c r="AF12">
+        <v>300480168786.346</v>
+      </c>
+      <c r="AG12">
+        <v>7.76063411026838</v>
+      </c>
+      <c r="AH12">
+        <v>49.2552064974161</v>
+      </c>
+      <c r="AI12">
         <v>7.652</v>
       </c>
+      <c r="AJ12">
+        <v>30.93</v>
+      </c>
+      <c r="AK12">
+        <v>0.443312972784042</v>
+      </c>
     </row>
-    <row r="13" spans="1:6">
+    <row r="13" spans="1:37">
       <c r="A13" s="1">
         <v>2011</v>
       </c>
       <c r="B13">
+        <v>5.86709064425737</v>
+      </c>
+      <c r="C13">
+        <v>2.67019501469286</v>
+      </c>
+      <c r="D13">
+        <v>-0.540835857391357</v>
+      </c>
+      <c r="E13">
+        <v>-3.42928468606061</v>
+      </c>
+      <c r="F13">
+        <v>51.5565536600977</v>
+      </c>
+      <c r="G13">
+        <v>51.2892331325447</v>
+      </c>
+      <c r="H13">
+        <v>24.5404113195713</v>
+      </c>
+      <c r="I13">
+        <v>18.5055609944676</v>
+      </c>
+      <c r="J13">
+        <v>334399298473.1</v>
+      </c>
+      <c r="K13">
         <v>5.24131619937695</v>
       </c>
-      <c r="C13">
+      <c r="L13">
+        <v>4454.70153200513</v>
+      </c>
+      <c r="M13">
+        <v>1445.46127486037</v>
+      </c>
+      <c r="N13">
+        <v>3.76074153145865</v>
+      </c>
+      <c r="O13">
+        <v>28.8</v>
+      </c>
+      <c r="P13">
+        <v>0.0225540697574615</v>
+      </c>
+      <c r="Q13">
+        <v>11.0844615855594</v>
+      </c>
+      <c r="R13">
+        <v>14.4898394030493</v>
+      </c>
+      <c r="S13">
+        <v>11.4959960090891</v>
+      </c>
+      <c r="T13">
+        <v>31.0834686939585</v>
+      </c>
+      <c r="U13">
         <v>8.9117933648337</v>
       </c>
-      <c r="D13">
+      <c r="V13">
         <v>18.1969064998262</v>
       </c>
-      <c r="E13">
+      <c r="W13">
+        <v>67.623</v>
+      </c>
+      <c r="X13">
+        <v>2.70448222276966</v>
+      </c>
+      <c r="Y13">
+        <v>-3.20649564885787</v>
+      </c>
+      <c r="Z13">
+        <v>-1.32679533958435</v>
+      </c>
+      <c r="AA13">
+        <v>1261224954</v>
+      </c>
+      <c r="AB13">
+        <v>27.1</v>
+      </c>
+      <c r="AC13">
+        <v>-0.363154947757721</v>
+      </c>
+      <c r="AD13">
+        <v>-0.0862971395254135</v>
+      </c>
+      <c r="AE13">
         <v>10.1773871997608</v>
       </c>
-      <c r="F13">
+      <c r="AF13">
+        <v>298739463090.872</v>
+      </c>
+      <c r="AG13">
+        <v>6.18879010347658</v>
+      </c>
+      <c r="AH13">
+        <v>55.6238800135298</v>
+      </c>
+      <c r="AI13">
         <v>7.616</v>
       </c>
+      <c r="AJ13">
+        <v>31.276</v>
+      </c>
+      <c r="AK13">
+        <v>0.435818582773209</v>
+      </c>
     </row>
-    <row r="14" spans="1:6">
+    <row r="14" spans="1:37">
       <c r="A14" s="1">
         <v>2012</v>
       </c>
       <c r="B14">
+        <v>6.1269010808579</v>
+      </c>
+      <c r="C14">
+        <v>3.37395391664123</v>
+      </c>
+      <c r="D14">
+        <v>-0.513968110084534</v>
+      </c>
+      <c r="E14">
+        <v>-5.00488971805303</v>
+      </c>
+      <c r="F14">
+        <v>50.6780305618952</v>
+      </c>
+      <c r="G14">
+        <v>51.8885076473464</v>
+      </c>
+      <c r="H14">
+        <v>24.534430661418</v>
+      </c>
+      <c r="I14">
+        <v>21.7351878662519</v>
+      </c>
+      <c r="J14">
+        <v>392576050359.7</v>
+      </c>
+      <c r="K14">
         <v>5.45638755166587</v>
       </c>
-      <c r="C14">
+      <c r="L14">
+        <v>4819.64288218731</v>
+      </c>
+      <c r="M14">
+        <v>1429.32199520032</v>
+      </c>
+      <c r="N14">
+        <v>4.01726735836323</v>
+      </c>
+      <c r="P14">
+        <v>-0.15608711540699</v>
+      </c>
+      <c r="Q14">
+        <v>10.6838562318127</v>
+      </c>
+      <c r="R14">
+        <v>16.166712404362</v>
+      </c>
+      <c r="S14">
+        <v>12.599872776486</v>
+      </c>
+      <c r="T14">
+        <v>31.2592910673332</v>
+      </c>
+      <c r="U14">
         <v>9.47899691419798</v>
       </c>
-      <c r="D14">
+      <c r="V14">
         <v>19.457832074744</v>
       </c>
-      <c r="E14">
+      <c r="W14">
+        <v>68.07599999999999</v>
+      </c>
+      <c r="X14">
+        <v>2.61816634758562</v>
+      </c>
+      <c r="Y14">
+        <v>-3.7644761333206</v>
+      </c>
+      <c r="Z14">
+        <v>-1.28930985927582</v>
+      </c>
+      <c r="AA14">
+        <v>1278674502</v>
+      </c>
+      <c r="AC14">
+        <v>-0.480885624885559</v>
+      </c>
+      <c r="AD14">
+        <v>-0.0628807470202446</v>
+      </c>
+      <c r="AE14">
         <v>10.8367717209692</v>
       </c>
-      <c r="F14">
+      <c r="AF14">
+        <v>300425517446.546</v>
+      </c>
+      <c r="AG14">
+        <v>5.90371509588661</v>
+      </c>
+      <c r="AH14">
+        <v>55.7937217287511</v>
+      </c>
+      <c r="AI14">
         <v>7.666</v>
       </c>
+      <c r="AJ14">
+        <v>31.634</v>
+      </c>
+      <c r="AK14">
+        <v>0.399454206228256</v>
+      </c>
     </row>
-    <row r="15" spans="1:6">
+    <row r="15" spans="1:37">
       <c r="A15" s="1">
         <v>2013</v>
       </c>
       <c r="B15">
+        <v>6.07239638921747</v>
+      </c>
+      <c r="C15">
+        <v>4.02772863501631</v>
+      </c>
+      <c r="D15">
+        <v>-0.517280995845795</v>
+      </c>
+      <c r="E15">
+        <v>-2.64566711733892</v>
+      </c>
+      <c r="F15">
+        <v>50.3118273627008</v>
+      </c>
+      <c r="G15">
+        <v>52.385709516972</v>
+      </c>
+      <c r="H15">
+        <v>25.430861300519</v>
+      </c>
+      <c r="I15">
+        <v>23.3008757774803</v>
+      </c>
+      <c r="J15">
+        <v>427245079805.9</v>
+      </c>
+      <c r="K15">
         <v>6.38610640094825</v>
       </c>
-      <c r="C15">
+      <c r="L15">
+        <v>5014.3505659078</v>
+      </c>
+      <c r="M15">
+        <v>1432.84397512195</v>
+      </c>
+      <c r="N15">
+        <v>4.97769997302639</v>
+      </c>
+      <c r="P15">
+        <v>-0.157355144619942</v>
+      </c>
+      <c r="Q15">
+        <v>10.2951601419598</v>
+      </c>
+      <c r="R15">
+        <v>16.6386825486965</v>
+      </c>
+      <c r="S15">
+        <v>12.6089934124693</v>
+      </c>
+      <c r="T15">
+        <v>28.4132706461587</v>
+      </c>
+      <c r="U15">
         <v>10.0178784746103</v>
       </c>
-      <c r="D15">
+      <c r="V15">
         <v>19.4875635997881</v>
       </c>
-      <c r="E15">
+      <c r="W15">
+        <v>68.499</v>
+      </c>
+      <c r="X15">
+        <v>2.5488248901417</v>
+      </c>
+      <c r="Y15">
+        <v>-4.06573304249265</v>
+      </c>
+      <c r="Z15">
+        <v>-1.22917413711548</v>
+      </c>
+      <c r="AA15">
+        <v>1295829511</v>
+      </c>
+      <c r="AC15">
+        <v>-0.478094786405563</v>
+      </c>
+      <c r="AD15">
+        <v>-0.0458925999701023</v>
+      </c>
+      <c r="AE15">
         <v>11.0016256942917</v>
       </c>
-      <c r="F15">
+      <c r="AF15">
+        <v>298092478740.581</v>
+      </c>
+      <c r="AG15">
+        <v>6.02774649537523</v>
+      </c>
+      <c r="AH15">
+        <v>53.8441319466777</v>
+      </c>
+      <c r="AI15">
         <v>7.711</v>
       </c>
+      <c r="AJ15">
+        <v>32.003</v>
+      </c>
+      <c r="AK15">
+        <v>0.432717055082321</v>
+      </c>
     </row>
-    <row r="16" spans="1:6">
+    <row r="16" spans="1:37">
       <c r="A16" s="1">
         <v>2014</v>
       </c>
       <c r="B16">
+        <v>6.31072146718646</v>
+      </c>
+      <c r="C16">
+        <v>4.34584976316209</v>
+      </c>
+      <c r="D16">
+        <v>-0.457605749368668</v>
+      </c>
+      <c r="E16">
+        <v>-1.33950896483453</v>
+      </c>
+      <c r="F16">
+        <v>49.9009248748319</v>
+      </c>
+      <c r="G16">
+        <v>51.8821873589628</v>
+      </c>
+      <c r="H16">
+        <v>22.9679630081172</v>
+      </c>
+      <c r="I16">
+        <v>22.7049198417658</v>
+      </c>
+      <c r="J16">
+        <v>457507409077.4</v>
+      </c>
+      <c r="K16">
         <v>7.41022760508854</v>
       </c>
-      <c r="C16">
+      <c r="L16">
+        <v>5191.59149903249</v>
+      </c>
+      <c r="M16">
+        <v>1553.88396075118</v>
+      </c>
+      <c r="N16">
+        <v>6.06398074162718</v>
+      </c>
+      <c r="P16">
+        <v>-0.222846582531929</v>
+      </c>
+      <c r="Q16">
+        <v>10.4408568081213</v>
+      </c>
+      <c r="R16">
+        <v>14.803137644208</v>
+      </c>
+      <c r="S16">
+        <v>11.550620644555</v>
+      </c>
+      <c r="T16">
+        <v>25.9542227389497</v>
+      </c>
+      <c r="U16">
         <v>6.66565671867896</v>
       </c>
-      <c r="D16">
+      <c r="V16">
         <v>21.2355969489067</v>
       </c>
-      <c r="E16">
+      <c r="W16">
+        <v>68.932</v>
+      </c>
+      <c r="X16">
+        <v>2.54398176462257</v>
+      </c>
+      <c r="Y16">
+        <v>-3.24743717876857</v>
+      </c>
+      <c r="Z16">
+        <v>-0.997911989688873</v>
+      </c>
+      <c r="AA16">
+        <v>1312277191</v>
+      </c>
+      <c r="AC16">
+        <v>-0.47507643699646</v>
+      </c>
+      <c r="AD16">
+        <v>-0.06918938457965849</v>
+      </c>
+      <c r="AE16">
         <v>9.984654190713121</v>
       </c>
-      <c r="F16">
+      <c r="AF16">
+        <v>325081035127.891</v>
+      </c>
+      <c r="AG16">
+        <v>6.5991330802017</v>
+      </c>
+      <c r="AH16">
+        <v>48.9221857470669</v>
+      </c>
+      <c r="AI16">
         <v>7.674</v>
       </c>
+      <c r="AJ16">
+        <v>32.384</v>
+      </c>
+      <c r="AK16">
+        <v>0.413222134113312</v>
+      </c>
     </row>
-    <row r="17" spans="1:6">
+    <row r="17" spans="1:37">
       <c r="A17" s="1">
         <v>2015</v>
       </c>
       <c r="B17">
+        <v>6.67847337958985</v>
+      </c>
+      <c r="C17">
+        <v>5.88352227400692</v>
+      </c>
+      <c r="D17">
+        <v>-0.406574189662933</v>
+      </c>
+      <c r="E17">
+        <v>-1.06754907167965</v>
+      </c>
+      <c r="F17">
+        <v>49.9647183856551</v>
+      </c>
+      <c r="G17">
+        <v>51.8675240772049</v>
+      </c>
+      <c r="H17">
+        <v>19.8131891564045</v>
+      </c>
+      <c r="I17">
+        <v>23.0297689509967</v>
+      </c>
+      <c r="J17">
+        <v>478831010025.1</v>
+      </c>
+      <c r="K17">
         <v>7.99625378571471</v>
       </c>
-      <c r="C17">
+      <c r="L17">
+        <v>5425.03599091046</v>
+      </c>
+      <c r="M17">
+        <v>1583.99815907985</v>
+      </c>
+      <c r="N17">
+        <v>6.71566734640226</v>
+      </c>
+      <c r="P17">
+        <v>0.08008150011301041</v>
+      </c>
+      <c r="Q17">
+        <v>10.4282907091862</v>
+      </c>
+      <c r="R17">
+        <v>15.1256903622794</v>
+      </c>
+      <c r="S17">
+        <v>12.4152095425778</v>
+      </c>
+      <c r="T17">
+        <v>22.1097247094602</v>
+      </c>
+      <c r="U17">
         <v>4.9069734412726</v>
       </c>
-      <c r="D17">
+      <c r="V17">
         <v>20.7148895559531</v>
       </c>
-      <c r="E17">
+      <c r="W17">
+        <v>69.32599999999999</v>
+      </c>
+      <c r="X17">
+        <v>2.45745006060163</v>
+      </c>
+      <c r="Y17">
+        <v>-2.77580962011863</v>
+      </c>
+      <c r="Z17">
+        <v>-0.954773545265198</v>
+      </c>
+      <c r="AA17">
+        <v>1328024498</v>
+      </c>
+      <c r="AC17">
+        <v>-0.4249567091465</v>
+      </c>
+      <c r="AD17">
+        <v>-0.0707211047410965</v>
+      </c>
+      <c r="AE17">
         <v>10.5697090519718</v>
       </c>
-      <c r="F17">
+      <c r="AF17">
+        <v>353319061013.224</v>
+      </c>
+      <c r="AG17">
+        <v>8.00309182929653</v>
+      </c>
+      <c r="AH17">
+        <v>41.9229138658647</v>
+      </c>
+      <c r="AI17">
         <v>7.631</v>
       </c>
+      <c r="AJ17">
+        <v>32.777</v>
+      </c>
+      <c r="AK17">
+        <v>0.427862852811813</v>
+      </c>
     </row>
-    <row r="18" spans="1:6">
+    <row r="18" spans="1:37">
       <c r="A18" s="1">
         <v>2016</v>
       </c>
       <c r="B18">
+        <v>6.70143866382393</v>
+      </c>
+      <c r="C18">
+        <v>9.185655918149569</v>
+      </c>
+      <c r="D18">
+        <v>-0.337335646152496</v>
+      </c>
+      <c r="E18">
+        <v>-0.52788060603752</v>
+      </c>
+      <c r="F18">
+        <v>47.6337555915272</v>
+      </c>
+      <c r="G18">
+        <v>49.1012254191449</v>
+      </c>
+      <c r="H18">
+        <v>19.1582349105946</v>
+      </c>
+      <c r="I18">
+        <v>20.0812235448632</v>
+      </c>
+      <c r="J18">
+        <v>455541896498.9</v>
+      </c>
+      <c r="K18">
         <v>8.256305501790861</v>
       </c>
-      <c r="C18">
+      <c r="L18">
+        <v>5800.48149366552</v>
+      </c>
+      <c r="M18">
+        <v>1707.50892912243</v>
+      </c>
+      <c r="N18">
+        <v>6.97394690929247</v>
+      </c>
+      <c r="P18">
+        <v>0.0613894164562225</v>
+      </c>
+      <c r="Q18">
+        <v>10.3085480747222</v>
+      </c>
+      <c r="R18">
+        <v>15.2719500252316</v>
+      </c>
+      <c r="S18">
+        <v>12.8510169890546</v>
+      </c>
+      <c r="T18">
+        <v>20.9242508026814</v>
+      </c>
+      <c r="U18">
         <v>4.94821634062135</v>
       </c>
-      <c r="D18">
+      <c r="V18">
         <v>20.3860448020257</v>
       </c>
-      <c r="E18">
+      <c r="W18">
+        <v>69.709</v>
+      </c>
+      <c r="X18">
+        <v>2.54315152114541</v>
+      </c>
+      <c r="Y18">
+        <v>-2.41851614428797</v>
+      </c>
+      <c r="Z18">
+        <v>-0.960426509380341</v>
+      </c>
+      <c r="AA18">
+        <v>1343944296</v>
+      </c>
+      <c r="AC18">
+        <v>-0.31153193116188</v>
+      </c>
+      <c r="AD18">
+        <v>-0.0561538562178612</v>
+      </c>
+      <c r="AE18">
         <v>11.1477384183764</v>
       </c>
-      <c r="F18">
+      <c r="AF18">
+        <v>361694321972.036</v>
+      </c>
+      <c r="AG18">
+        <v>8.43013905768235</v>
+      </c>
+      <c r="AH18">
+        <v>40.082485713276</v>
+      </c>
+      <c r="AI18">
         <v>7.601</v>
       </c>
+      <c r="AJ18">
+        <v>33.182</v>
+      </c>
+      <c r="AK18">
+        <v>0.441010862588882</v>
+      </c>
     </row>
-    <row r="19" spans="1:6">
+    <row r="19" spans="1:37">
       <c r="A19" s="1">
         <v>2017</v>
       </c>
       <c r="B19">
+        <v>7.04073187631062</v>
+      </c>
+      <c r="C19">
+        <v>9.975282063631781</v>
+      </c>
+      <c r="D19">
+        <v>-0.291900008916855</v>
+      </c>
+      <c r="E19">
+        <v>-1.43948820320989</v>
+      </c>
+      <c r="F19">
+        <v>47.5836093800197</v>
+      </c>
+      <c r="G19">
+        <v>48.7940213990706</v>
+      </c>
+      <c r="H19">
+        <v>18.7917648392982</v>
+      </c>
+      <c r="I19">
+        <v>19.5049373712632</v>
+      </c>
+      <c r="J19">
+        <v>511575707373.6</v>
+      </c>
+      <c r="K19">
         <v>6.79538341897911</v>
       </c>
-      <c r="C19">
+      <c r="L19">
+        <v>6144.71714444938</v>
+      </c>
+      <c r="M19">
+        <v>1950.10468280866</v>
+      </c>
+      <c r="N19">
+        <v>5.561185034605</v>
+      </c>
+      <c r="P19">
+        <v>0.0410966314375401</v>
+      </c>
+      <c r="Q19">
+        <v>10.7671989547856</v>
+      </c>
+      <c r="R19">
+        <v>15.6141099220983</v>
+      </c>
+      <c r="S19">
+        <v>12.7267619005257</v>
+      </c>
+      <c r="T19">
+        <v>21.9507321152243</v>
+      </c>
+      <c r="U19">
         <v>3.328173374613</v>
       </c>
-      <c r="D19">
+      <c r="V19">
         <v>19.8334019122654</v>
       </c>
-      <c r="E19">
+      <c r="W19">
+        <v>70.068</v>
+      </c>
+      <c r="X19">
+        <v>2.53151136056791</v>
+      </c>
+      <c r="Y19">
+        <v>-2.55426517252434</v>
+      </c>
+      <c r="Z19">
+        <v>-0.7740991115570069</v>
+      </c>
+      <c r="AA19">
+        <v>1359657400</v>
+      </c>
+      <c r="AC19">
+        <v>-0.256661295890808</v>
+      </c>
+      <c r="AD19">
+        <v>-0.0297500882297754</v>
+      </c>
+      <c r="AE19">
         <v>11.3874439798131</v>
       </c>
-      <c r="F19">
+      <c r="AF19">
+        <v>412613792019.924</v>
+      </c>
+      <c r="AG19">
+        <v>8.162718669436281</v>
+      </c>
+      <c r="AH19">
+        <v>40.7424969545225</v>
+      </c>
+      <c r="AI19">
         <v>7.618</v>
       </c>
+      <c r="AJ19">
+        <v>33.6</v>
+      </c>
+      <c r="AK19">
+        <v>0.386967867612839</v>
+      </c>
     </row>
-    <row r="20" spans="1:6">
+    <row r="20" spans="1:37">
       <c r="A20" s="1">
         <v>2018</v>
       </c>
       <c r="B20">
+        <v>6.89425620584035</v>
+      </c>
+      <c r="C20">
+        <v>9.46095691207992</v>
+      </c>
+      <c r="D20">
+        <v>-0.229758977890015</v>
+      </c>
+      <c r="E20">
+        <v>-2.42697545810527</v>
+      </c>
+      <c r="F20">
+        <v>46.5224986659322</v>
+      </c>
+      <c r="G20">
+        <v>50.3381627463062</v>
+      </c>
+      <c r="H20">
+        <v>19.9278285988562</v>
+      </c>
+      <c r="I20">
+        <v>19.4905310721105</v>
+      </c>
+      <c r="J20">
+        <v>521175685410</v>
+      </c>
+      <c r="K20">
         <v>6.45385134497769</v>
       </c>
-      <c r="C20">
+      <c r="L20">
+        <v>6714.96639877754</v>
+      </c>
+      <c r="M20">
+        <v>1966.25455171679</v>
+      </c>
+      <c r="N20">
+        <v>5.29211971914722</v>
+      </c>
+      <c r="P20">
+        <v>0.262917786836624</v>
+      </c>
+      <c r="Q20">
+        <v>10.8232185258548</v>
+      </c>
+      <c r="R20">
+        <v>15.6631319151388</v>
+      </c>
+      <c r="S20">
+        <v>13.1885329486481</v>
+      </c>
+      <c r="T20">
+        <v>23.6891407335327</v>
+      </c>
+      <c r="U20">
         <v>3.93882646691633</v>
       </c>
-      <c r="D20">
+      <c r="V20">
         <v>19.3965097896145</v>
       </c>
-      <c r="E20">
+      <c r="W20">
+        <v>70.41500000000001</v>
+      </c>
+      <c r="X20">
+        <v>2.42428452604417</v>
+      </c>
+      <c r="Y20">
+        <v>-2.30328908296065</v>
+      </c>
+      <c r="Z20">
+        <v>-0.997706770896912</v>
+      </c>
+      <c r="AA20">
+        <v>1374659064</v>
+      </c>
+      <c r="AC20">
+        <v>-0.225996732711792</v>
+      </c>
+      <c r="AD20">
+        <v>-0.00142208894249052</v>
+      </c>
+      <c r="AE20">
         <v>12.0174277483166</v>
       </c>
-      <c r="F20">
+      <c r="AF20">
+        <v>399167159226.682</v>
+      </c>
+      <c r="AG20">
+        <v>6.90105548512364</v>
+      </c>
+      <c r="AH20">
+        <v>43.6169693323889</v>
+      </c>
+      <c r="AI20">
         <v>7.652</v>
       </c>
+      <c r="AJ20">
+        <v>34.03</v>
+      </c>
+      <c r="AK20">
+        <v>0.360422104597092</v>
+      </c>
     </row>
-    <row r="21" spans="1:6">
+    <row r="21" spans="1:37">
       <c r="A21" s="1">
         <v>2019</v>
       </c>
       <c r="B21">
+        <v>8.025361607422481</v>
+      </c>
+      <c r="C21">
+        <v>9.23442899080834</v>
+      </c>
+      <c r="D21">
+        <v>-0.30260244011879</v>
+      </c>
+      <c r="E21">
+        <v>-1.04961203910072</v>
+      </c>
+      <c r="G21">
+        <v>50.7424617406439</v>
+      </c>
+      <c r="H21">
+        <v>18.664264897257</v>
+      </c>
+      <c r="I21">
+        <v>19.9766366353145</v>
+      </c>
+      <c r="J21">
+        <v>561017395481.3</v>
+      </c>
+      <c r="K21">
         <v>3.87143694070356</v>
       </c>
-      <c r="C21">
+      <c r="L21">
+        <v>7150.92423452926</v>
+      </c>
+      <c r="M21">
+        <v>2041.42863698585</v>
+      </c>
+      <c r="N21">
+        <v>2.79675759965889</v>
+      </c>
+      <c r="P21">
+        <v>0.130771830677986</v>
+      </c>
+      <c r="Q21">
+        <v>11.0026755133718</v>
+      </c>
+      <c r="T21">
+        <v>21.2411386333872</v>
+      </c>
+      <c r="U21">
         <v>3.72950573539127</v>
       </c>
-      <c r="F21">
+      <c r="W21">
+        <v>70.746</v>
+      </c>
+      <c r="X21">
+        <v>2.5459982314359</v>
+      </c>
+      <c r="Z21">
+        <v>-0.796846985816956</v>
+      </c>
+      <c r="AA21">
+        <v>1389030312</v>
+      </c>
+      <c r="AC21">
+        <v>-0.150565445423126</v>
+      </c>
+      <c r="AD21">
+        <v>-0.0672271549701691</v>
+      </c>
+      <c r="AF21">
+        <v>463469902152.507</v>
+      </c>
+      <c r="AG21">
+        <v>8.273659400483959</v>
+      </c>
+      <c r="AH21">
+        <v>39.9054035306442</v>
+      </c>
+      <c r="AI21">
         <v>6.51</v>
       </c>
+      <c r="AJ21">
+        <v>34.472</v>
+      </c>
+      <c r="AK21">
+        <v>0.268077671527863</v>
+      </c>
     </row>
-    <row r="22" spans="1:6">
+    <row r="22" spans="1:37">
       <c r="A22" s="1">
         <v>2020</v>
       </c>
       <c r="B22">
+        <v>7.81226700977292</v>
+      </c>
+      <c r="C22">
+        <v>7.93883072465331</v>
+      </c>
+      <c r="D22">
+        <v>-0.293598413467407</v>
+      </c>
+      <c r="E22">
+        <v>1.22362111042791</v>
+      </c>
+      <c r="G22">
+        <v>54.5052902460387</v>
+      </c>
+      <c r="H22">
+        <v>18.6824769296756</v>
+      </c>
+      <c r="I22">
+        <v>21.4094740100862</v>
+      </c>
+      <c r="J22">
+        <v>564979321177.1</v>
+      </c>
+      <c r="K22">
         <v>-5.77772470686801</v>
       </c>
-      <c r="C22">
+      <c r="L22">
+        <v>6966.27542785911</v>
+      </c>
+      <c r="M22">
+        <v>1907.04251637669</v>
+      </c>
+      <c r="N22">
+        <v>-6.69047102833747</v>
+      </c>
+      <c r="P22">
+        <v>0.374532461166382</v>
+      </c>
+      <c r="Q22">
+        <v>11.6124524106018</v>
+      </c>
+      <c r="T22">
+        <v>19.0756283996012</v>
+      </c>
+      <c r="U22">
         <v>6.62343677628536</v>
       </c>
-      <c r="F22">
+      <c r="W22">
+        <v>70.15600000000001</v>
+      </c>
+      <c r="X22">
+        <v>2.80719387386131</v>
+      </c>
+      <c r="Z22">
+        <v>-0.841419219970703</v>
+      </c>
+      <c r="AA22">
+        <v>1402617695</v>
+      </c>
+      <c r="AC22">
+        <v>-0.128488674759865</v>
+      </c>
+      <c r="AD22">
+        <v>-0.0584247447550297</v>
+      </c>
+      <c r="AF22">
+        <v>590227359928.896</v>
+      </c>
+      <c r="AG22">
+        <v>12.9323281065786</v>
+      </c>
+      <c r="AH22">
+        <v>37.7581053292768</v>
+      </c>
+      <c r="AI22">
         <v>7.859</v>
       </c>
+      <c r="AJ22">
+        <v>34.926</v>
+      </c>
+      <c r="AK22">
+        <v>0.127332791686058</v>
+      </c>
     </row>
-    <row r="23" spans="1:6">
+    <row r="23" spans="1:37">
       <c r="A23" s="1">
         <v>2021</v>
       </c>
       <c r="B23">
+        <v>7.82632507203676</v>
+      </c>
+      <c r="C23">
+        <v>6.54245582956179</v>
+      </c>
+      <c r="D23">
+        <v>-0.317147105932236</v>
+      </c>
+      <c r="E23">
+        <v>-1.05524166809383</v>
+      </c>
+      <c r="G23">
+        <v>50.1421581396983</v>
+      </c>
+      <c r="H23">
+        <v>21.3991583305515</v>
+      </c>
+      <c r="I23">
+        <v>19.5524130311129</v>
+      </c>
+      <c r="J23">
+        <v>611987174447.7</v>
+      </c>
+      <c r="K23">
         <v>9.689592491928749</v>
       </c>
-      <c r="C23">
+      <c r="L23">
+        <v>8050.01857452664</v>
+      </c>
+      <c r="M23">
+        <v>2239.61384367482</v>
+      </c>
+      <c r="N23">
+        <v>8.790934476762629</v>
+      </c>
+      <c r="P23">
+        <v>0.249238416552544</v>
+      </c>
+      <c r="Q23">
+        <v>10.4763782400684</v>
+      </c>
+      <c r="T23">
+        <v>24.0239304534931</v>
+      </c>
+      <c r="U23">
         <v>5.13140747176368</v>
       </c>
-      <c r="F23">
+      <c r="W23">
+        <v>67.282</v>
+      </c>
+      <c r="X23">
+        <v>2.48038870521367</v>
+      </c>
+      <c r="Z23">
+        <v>-0.691076755523682</v>
+      </c>
+      <c r="AA23">
+        <v>1414203896</v>
+      </c>
+      <c r="AC23">
+        <v>-0.0908545926213264</v>
+      </c>
+      <c r="AD23">
+        <v>-0.108451806008816</v>
+      </c>
+      <c r="AF23">
+        <v>638484779930.8361</v>
+      </c>
+      <c r="AG23">
+        <v>9.842385744523281</v>
+      </c>
+      <c r="AH23">
+        <v>45.4230887840446</v>
+      </c>
+      <c r="AI23">
         <v>6.38</v>
       </c>
+      <c r="AJ23">
+        <v>35.393</v>
+      </c>
+      <c r="AK23">
+        <v>0.0905434712767601</v>
+      </c>
     </row>
-    <row r="24" spans="1:6">
+    <row r="24" spans="1:37">
       <c r="A24" s="1">
         <v>2022</v>
       </c>
       <c r="B24">
+        <v>7.75637955901566</v>
+      </c>
+      <c r="C24">
+        <v>4.81188453965167</v>
+      </c>
+      <c r="D24">
+        <v>-0.322223275899887</v>
+      </c>
+      <c r="E24">
+        <v>-2.36247481487452</v>
+      </c>
+      <c r="H24">
+        <v>23.2515412045298</v>
+      </c>
+      <c r="I24">
+        <v>18.6103165564092</v>
+      </c>
+      <c r="J24">
+        <v>615516027421.2</v>
+      </c>
+      <c r="K24">
         <v>7.60936497768895</v>
       </c>
-      <c r="C24">
+      <c r="L24">
+        <v>9207.12743040145</v>
+      </c>
+      <c r="M24">
+        <v>2347.44829434623</v>
+      </c>
+      <c r="N24">
+        <v>6.76238601727897</v>
+      </c>
+      <c r="O24">
+        <v>25.5</v>
+      </c>
+      <c r="P24">
+        <v>0.369541674852371</v>
+      </c>
+      <c r="Q24">
+        <v>10.255037910793</v>
+      </c>
+      <c r="R24">
+        <v>13.3335178491336</v>
+      </c>
+      <c r="S24">
+        <v>9.11011784382656</v>
+      </c>
+      <c r="T24">
+        <v>26.8237289453584</v>
+      </c>
+      <c r="U24">
         <v>6.69903414079849</v>
       </c>
-      <c r="D24">
+      <c r="V24">
         <v>23.2265929898439</v>
       </c>
-      <c r="E24">
+      <c r="W24">
+        <v>71.69799999999999</v>
+      </c>
+      <c r="X24">
+        <v>2.36392657703578</v>
+      </c>
+      <c r="Y24">
+        <v>-5.10885108605465</v>
+      </c>
+      <c r="Z24">
+        <v>-0.615027368068695</v>
+      </c>
+      <c r="AA24">
+        <v>1425423212</v>
+      </c>
+      <c r="AB24">
+        <v>5.3</v>
+      </c>
+      <c r="AC24">
+        <v>-0.0504464171826839</v>
+      </c>
+      <c r="AD24">
+        <v>0.113943412899971</v>
+      </c>
+      <c r="AE24">
         <v>6.73444285965496</v>
       </c>
-      <c r="F24">
+      <c r="AF24">
+        <v>567298153917.14</v>
+      </c>
+      <c r="AG24">
+        <v>7.00951210544359</v>
+      </c>
+      <c r="AH24">
+        <v>50.0752701498882</v>
+      </c>
+      <c r="AI24">
         <v>4.822</v>
       </c>
+      <c r="AJ24">
+        <v>35.872</v>
+      </c>
+      <c r="AK24">
+        <v>0.0458774901926517</v>
+      </c>
     </row>
-    <row r="25" spans="1:6">
+    <row r="25" spans="1:37">
       <c r="A25" s="1">
         <v>2023</v>
       </c>
       <c r="B25">
+        <v>6.0839597444749</v>
+      </c>
+      <c r="C25">
+        <v>1.72349942158171</v>
+      </c>
+      <c r="D25">
+        <v>-0.366014748811722</v>
+      </c>
+      <c r="E25">
+        <v>-0.878262847208682</v>
+      </c>
+      <c r="H25">
+        <v>21.4486977833541</v>
+      </c>
+      <c r="I25">
+        <v>18.398392023483</v>
+      </c>
+      <c r="J25">
+        <v>646787065275.4</v>
+      </c>
+      <c r="K25">
         <v>9.19075493028345</v>
       </c>
-      <c r="C25">
+      <c r="L25">
+        <v>10323.4998734428</v>
+      </c>
+      <c r="M25">
+        <v>2530.12031278204</v>
+      </c>
+      <c r="N25">
+        <v>8.23053143349361</v>
+      </c>
+      <c r="P25">
+        <v>0.47511014342308</v>
+      </c>
+      <c r="Q25">
+        <v>10.3054222433801</v>
+      </c>
+      <c r="T25">
+        <v>23.544144504402</v>
+      </c>
+      <c r="U25">
         <v>5.64914318907929</v>
       </c>
-      <c r="F25">
+      <c r="W25">
+        <v>72.003</v>
+      </c>
+      <c r="X25">
+        <v>2.44305076476938</v>
+      </c>
+      <c r="Z25">
+        <v>-0.635076940059662</v>
+      </c>
+      <c r="AA25">
+        <v>1438069596</v>
+      </c>
+      <c r="AC25">
+        <v>-0.136969581246376</v>
+      </c>
+      <c r="AD25">
+        <v>0.188364565372467</v>
+      </c>
+      <c r="AF25">
+        <v>627792750126.715</v>
+      </c>
+      <c r="AG25">
+        <v>7.97237314389747</v>
+      </c>
+      <c r="AH25">
+        <v>44.9928422877561</v>
+      </c>
+      <c r="AI25">
         <v>4.172</v>
       </c>
+      <c r="AJ25">
+        <v>36.364</v>
+      </c>
+      <c r="AK25">
+        <v>0.0944044888019562</v>
+      </c>
     </row>
-    <row r="26" spans="1:6">
+    <row r="26" spans="1:37">
       <c r="A26" s="1">
         <v>2024</v>
       </c>
-      <c r="B26">
+      <c r="E26">
+        <v>-0.821660552648862</v>
+      </c>
+      <c r="H26">
+        <v>21.1781223210845</v>
+      </c>
+      <c r="K26">
         <v>6.48422363033757</v>
       </c>
-      <c r="C26">
+      <c r="L26">
+        <v>11158.8809230756</v>
+      </c>
+      <c r="M26">
+        <v>2696.66389984463</v>
+      </c>
+      <c r="N26">
+        <v>5.53997317201281</v>
+      </c>
+      <c r="Q26">
+        <v>10.1442293317158</v>
+      </c>
+      <c r="T26">
+        <v>23.4929703141577</v>
+      </c>
+      <c r="U26">
         <v>4.95303550973652</v>
       </c>
-      <c r="F26">
+      <c r="AA26">
+        <v>1450935791</v>
+      </c>
+      <c r="AF26">
+        <v>643042560625.541</v>
+      </c>
+      <c r="AG26">
+        <v>7.52133677782434</v>
+      </c>
+      <c r="AH26">
+        <v>44.6710926352422</v>
+      </c>
+      <c r="AI26">
         <v>4.202</v>
+      </c>
+      <c r="AJ26">
+        <v>36.867</v>
       </c>
     </row>
   </sheetData>
